--- a/data/advisor/qiriness-knowledge-template.xlsx
+++ b/data/advisor/qiriness-knowledge-template.xlsx
@@ -10809,7 +10809,7 @@
         <v>72</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="H93" s="21"/>
       <c r="I93" s="15"/>
